--- a/Analysis/Top20_Feature_Combinations_SVM.xlsx
+++ b/Analysis/Top20_Feature_Combinations_SVM.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,35 +441,45 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>N Features</t>
+          <t>Behavioral Features</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>DDM Features</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Total Features</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>ADHD Correct (%)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Control Correct (%)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Overall Accuracy (%)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Balanced Accuracy (%)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>ROC-AUC</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
@@ -481,29 +491,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>commission_rate + d_prime</t>
+          <t>rt_mean + omission_rate + commission_rate + a</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>79.59183673469387</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>74.74747474747475</v>
+        <v>78</v>
       </c>
       <c r="G2" t="n">
-        <v>74.79591836734694</v>
+        <v>80.85106382978722</v>
       </c>
       <c r="H2" t="n">
-        <v>0.7681632653061224</v>
+        <v>79.38144329896907</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7368421052631579</v>
+        <v>79.42553191489361</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.8017021276595745</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.7959183673469388</v>
       </c>
     </row>
     <row r="3">
@@ -512,29 +528,35 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>accuracy + commission_rate</t>
+          <t>rt_mean + rt_std + omission_rate + commission_rate + d_prime + a + t</t>
         </is>
       </c>
       <c r="C3" t="n">
+        <v>5</v>
+      </c>
+      <c r="D3" t="n">
         <v>2</v>
       </c>
-      <c r="D3" t="n">
-        <v>68</v>
-      </c>
       <c r="E3" t="n">
-        <v>79.59183673469387</v>
+        <v>7</v>
       </c>
       <c r="F3" t="n">
-        <v>73.73737373737373</v>
+        <v>72</v>
       </c>
       <c r="G3" t="n">
-        <v>73.79591836734693</v>
+        <v>82.97872340425532</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7677551020408163</v>
+        <v>77.31958762886599</v>
       </c>
       <c r="I3" t="n">
-        <v>0.723404255319149</v>
+        <v>77.48936170212765</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.7919148936170213</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.7659574468085106</v>
       </c>
     </row>
     <row r="4">
@@ -543,29 +565,35 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>omission_rate + commission_rate</t>
+          <t>rt_mean + rt_std + accuracy + omission_rate + commission_rate + t</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>77.55102040816327</v>
+        <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>73.73737373737373</v>
+        <v>74</v>
       </c>
       <c r="G4" t="n">
-        <v>73.77551020408163</v>
+        <v>80.85106382978722</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7693877551020408</v>
+        <v>77.31958762886599</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7291666666666666</v>
+        <v>77.42553191489361</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.8029787234042554</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.7708333333333334</v>
       </c>
     </row>
     <row r="5">
@@ -574,29 +602,35 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>rt_std + accuracy</t>
+          <t>rt_mean + rt_std + omission_rate + commission_rate + d_prime + t</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>83.67346938775511</v>
+        <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>72.72727272727273</v>
+        <v>74</v>
       </c>
       <c r="G5" t="n">
-        <v>72.83673469387755</v>
+        <v>80.85106382978722</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7714285714285715</v>
+        <v>77.31958762886599</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6966292134831461</v>
+        <v>77.42553191489361</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.7948936170212765</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.7708333333333334</v>
       </c>
     </row>
     <row r="6">
@@ -605,29 +639,35 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>accuracy + omission_rate + commission_rate + d_prime</t>
+          <t>rt_mean + rt_std + accuracy + commission_rate + d_prime + a + t</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>66</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>79.59183673469387</v>
+        <v>7</v>
       </c>
       <c r="F6" t="n">
-        <v>72.72727272727273</v>
+        <v>74</v>
       </c>
       <c r="G6" t="n">
-        <v>72.79591836734693</v>
+        <v>80.85106382978722</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7718367346938775</v>
+        <v>77.31958762886599</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7096774193548387</v>
+        <v>77.42553191489361</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.7829787234042553</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.7708333333333334</v>
       </c>
     </row>
     <row r="7">
@@ -636,29 +676,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>accuracy + omission_rate + commission_rate</t>
+          <t>rt_mean + accuracy + commission_rate + a</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>3</v>
       </c>
       <c r="D7" t="n">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>79.59183673469387</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
-        <v>72.72727272727273</v>
+        <v>76</v>
       </c>
       <c r="G7" t="n">
-        <v>72.79591836734693</v>
+        <v>78.72340425531915</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7710204081632652</v>
+        <v>77.31958762886599</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7096774193548387</v>
+        <v>77.36170212765958</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.7961702127659573</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.7755102040816326</v>
       </c>
     </row>
     <row r="8">
@@ -667,29 +713,35 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>omission_rate + commission_rate + d_prime</t>
+          <t>rt_mean + omission_rate + commission_rate + d_prime + t</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D8" t="n">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>79.59183673469387</v>
+        <v>5</v>
       </c>
       <c r="F8" t="n">
-        <v>72.72727272727273</v>
+        <v>76</v>
       </c>
       <c r="G8" t="n">
-        <v>72.79591836734693</v>
+        <v>78.72340425531915</v>
       </c>
       <c r="H8" t="n">
-        <v>0.7706122448979592</v>
+        <v>77.31958762886599</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7096774193548387</v>
+        <v>77.36170212765958</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.7936170212765956</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.7755102040816326</v>
       </c>
     </row>
     <row r="9">
@@ -698,29 +750,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>accuracy + commission_rate + d_prime</t>
+          <t>rt_mean + accuracy + omission_rate + commission_rate + d_prime + t</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>79.59183673469387</v>
+        <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>72.72727272727273</v>
+        <v>76</v>
       </c>
       <c r="G9" t="n">
-        <v>72.79591836734693</v>
+        <v>78.72340425531915</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7685714285714286</v>
+        <v>77.31958762886599</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7096774193548387</v>
+        <v>77.36170212765958</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.7893617021276597</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.7755102040816326</v>
       </c>
     </row>
     <row r="10">
@@ -729,29 +787,35 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>rt_mean + rt_std + accuracy</t>
+          <t>rt_mean + d_prime + a + t</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>77.55102040816327</v>
+        <v>4</v>
       </c>
       <c r="F10" t="n">
-        <v>72.72727272727273</v>
+        <v>76</v>
       </c>
       <c r="G10" t="n">
-        <v>72.77551020408164</v>
+        <v>78.72340425531915</v>
       </c>
       <c r="H10" t="n">
-        <v>0.746734693877551</v>
+        <v>77.31958762886599</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7157894736842105</v>
+        <v>77.36170212765958</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.7859574468085107</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.7755102040816326</v>
       </c>
     </row>
     <row r="11">
@@ -760,29 +824,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>rt_std + omission_rate + commission_rate</t>
+          <t>accuracy + commission_rate + a</t>
         </is>
       </c>
       <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
         <v>3</v>
       </c>
-      <c r="D11" t="n">
-        <v>70</v>
-      </c>
-      <c r="E11" t="n">
-        <v>75.51020408163265</v>
-      </c>
       <c r="F11" t="n">
-        <v>72.72727272727273</v>
+        <v>76</v>
       </c>
       <c r="G11" t="n">
-        <v>72.75510204081633</v>
+        <v>78.72340425531915</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7583673469387756</v>
+        <v>77.31958762886599</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7216494845360825</v>
+        <v>77.36170212765958</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.7740425531914894</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.7755102040816326</v>
       </c>
     </row>
     <row r="12">
@@ -791,29 +861,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>rt_std + accuracy + commission_rate</t>
+          <t>accuracy + commission_rate + t</t>
         </is>
       </c>
       <c r="C12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
         <v>3</v>
       </c>
-      <c r="D12" t="n">
+      <c r="F12" t="n">
         <v>70</v>
       </c>
-      <c r="E12" t="n">
-        <v>75.51020408163265</v>
-      </c>
-      <c r="F12" t="n">
-        <v>72.72727272727273</v>
-      </c>
       <c r="G12" t="n">
-        <v>72.75510204081633</v>
+        <v>82.97872340425532</v>
       </c>
       <c r="H12" t="n">
-        <v>0.7551020408163265</v>
+        <v>76.28865979381443</v>
       </c>
       <c r="I12" t="n">
-        <v>0.7216494845360825</v>
+        <v>76.48936170212765</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.7540425531914894</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.7526881720430108</v>
       </c>
     </row>
     <row r="13">
@@ -822,29 +898,35 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>rt_mean + rt_std + commission_rate</t>
+          <t>rt_mean + rt_std + omission_rate + commission_rate + t</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>74</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>71.42857142857143</v>
+        <v>5</v>
       </c>
       <c r="F13" t="n">
-        <v>72.72727272727273</v>
+        <v>72</v>
       </c>
       <c r="G13" t="n">
-        <v>72.71428571428571</v>
+        <v>80.85106382978722</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7240816326530612</v>
+        <v>76.28865979381443</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7326732673267327</v>
+        <v>76.42553191489361</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.8004255319148936</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.7578947368421053</v>
       </c>
     </row>
     <row r="14">
@@ -853,29 +935,35 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>rt_std + accuracy + omission_rate + commission_rate</t>
+          <t>rt_mean + rt_std + accuracy + omission_rate + commission_rate + a + t</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>66</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>77.55102040816327</v>
+        <v>7</v>
       </c>
       <c r="F14" t="n">
-        <v>71.71717171717171</v>
+        <v>72</v>
       </c>
       <c r="G14" t="n">
-        <v>71.77551020408164</v>
+        <v>80.85106382978722</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7616326530612244</v>
+        <v>76.28865979381443</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7021276595744681</v>
+        <v>76.42553191489361</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.7982978723404255</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.7578947368421053</v>
       </c>
     </row>
     <row r="15">
@@ -884,29 +972,35 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>rt_mean + rt_std + accuracy + omission_rate</t>
+          <t>rt_mean + accuracy + commission_rate + d_prime + t</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>4</v>
       </c>
       <c r="D15" t="n">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>77.55102040816327</v>
+        <v>5</v>
       </c>
       <c r="F15" t="n">
-        <v>71.71717171717171</v>
+        <v>72</v>
       </c>
       <c r="G15" t="n">
-        <v>71.77551020408164</v>
+        <v>80.85106382978722</v>
       </c>
       <c r="H15" t="n">
-        <v>0.756734693877551</v>
+        <v>76.28865979381443</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7021276595744681</v>
+        <v>76.42553191489361</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.7817021276595744</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.7578947368421053</v>
       </c>
     </row>
     <row r="16">
@@ -915,29 +1009,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>rt_std + commission_rate + d_prime</t>
+          <t>rt_mean + omission_rate + commission_rate + d_prime + a + t</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D16" t="n">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>75.51020408163265</v>
+        <v>6</v>
       </c>
       <c r="F16" t="n">
-        <v>71.71717171717171</v>
+        <v>74</v>
       </c>
       <c r="G16" t="n">
-        <v>71.75510204081633</v>
+        <v>78.72340425531915</v>
       </c>
       <c r="H16" t="n">
-        <v>0.7465306122448979</v>
+        <v>76.28865979381443</v>
       </c>
       <c r="I16" t="n">
-        <v>0.7083333333333334</v>
+        <v>76.36170212765958</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.7910638297872341</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.7628865979381443</v>
       </c>
     </row>
     <row r="17">
@@ -946,29 +1046,35 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>rt_mean + accuracy + omission_rate</t>
+          <t>rt_mean + rt_std + accuracy + omission_rate + commission_rate + d_prime + t</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D17" t="n">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>77.55102040816327</v>
+        <v>7</v>
       </c>
       <c r="F17" t="n">
-        <v>70.70707070707071</v>
+        <v>74</v>
       </c>
       <c r="G17" t="n">
-        <v>70.77551020408164</v>
+        <v>78.72340425531915</v>
       </c>
       <c r="H17" t="n">
-        <v>0.76</v>
+        <v>76.28865979381443</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6881720430107527</v>
+        <v>76.36170212765958</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.7891489361702128</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.7628865979381443</v>
       </c>
     </row>
     <row r="18">
@@ -977,29 +1083,35 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>rt_mean + accuracy + omission_rate + commission_rate + d_prime</t>
+          <t>rt_mean + rt_std + accuracy + omission_rate + commission_rate + d_prime + a + t</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D18" t="n">
-        <v>64</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>77.55102040816327</v>
+        <v>8</v>
       </c>
       <c r="F18" t="n">
-        <v>70.70707070707071</v>
+        <v>74</v>
       </c>
       <c r="G18" t="n">
-        <v>70.77551020408164</v>
+        <v>78.72340425531915</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7579591836734694</v>
+        <v>76.28865979381443</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6881720430107527</v>
+        <v>76.36170212765958</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.7868085106382978</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.7628865979381443</v>
       </c>
     </row>
     <row r="19">
@@ -1008,29 +1120,35 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>rt_mean + accuracy + omission_rate + commission_rate</t>
+          <t>rt_mean + rt_std + accuracy + commission_rate + d_prime + t</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D19" t="n">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>75.51020408163265</v>
+        <v>6</v>
       </c>
       <c r="F19" t="n">
-        <v>70.70707070707071</v>
+        <v>74</v>
       </c>
       <c r="G19" t="n">
-        <v>70.75510204081633</v>
+        <v>78.72340425531915</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7591836734693879</v>
+        <v>76.28865979381443</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6947368421052632</v>
+        <v>76.36170212765958</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.7863829787234042</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.7628865979381443</v>
       </c>
     </row>
     <row r="20">
@@ -1039,29 +1157,35 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>rt_std + accuracy + omission_rate + commission_rate + d_prime</t>
+          <t>rt_mean + accuracy + commission_rate + d_prime + a</t>
         </is>
       </c>
       <c r="C20" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
         <v>5</v>
       </c>
-      <c r="D20" t="n">
-        <v>66</v>
-      </c>
-      <c r="E20" t="n">
-        <v>75.51020408163265</v>
-      </c>
       <c r="F20" t="n">
-        <v>70.70707070707071</v>
+        <v>74</v>
       </c>
       <c r="G20" t="n">
-        <v>70.75510204081633</v>
+        <v>78.72340425531915</v>
       </c>
       <c r="H20" t="n">
-        <v>0.7555102040816327</v>
+        <v>76.28865979381443</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6947368421052632</v>
+        <v>76.36170212765958</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.7817021276595744</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.7628865979381443</v>
       </c>
     </row>
     <row r="21">
@@ -1070,29 +1194,35 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>rt_mean + rt_std + accuracy + omission_rate + commission_rate + d_prime</t>
+          <t>rt_mean + rt_std + commission_rate + d_prime + a + t</t>
         </is>
       </c>
       <c r="C21" t="n">
+        <v>4</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
         <v>6</v>
       </c>
-      <c r="D21" t="n">
-        <v>66</v>
-      </c>
-      <c r="E21" t="n">
-        <v>75.51020408163265</v>
-      </c>
       <c r="F21" t="n">
-        <v>70.70707070707071</v>
+        <v>74</v>
       </c>
       <c r="G21" t="n">
-        <v>70.75510204081633</v>
+        <v>78.72340425531915</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7530612244897958</v>
+        <v>76.28865979381443</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6947368421052632</v>
+        <v>76.36170212765958</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.7799999999999999</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.7628865979381443</v>
       </c>
     </row>
   </sheetData>
